--- a/outputs/42526.xlsx
+++ b/outputs/42526.xlsx
@@ -120,24 +120,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -393,212 +397,212 @@
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30.89"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B2" s="2" t="n">
-        <f aca="false">IF(A2&gt;=0, 5*A2/41, 5*A2/18)</f>
+      <c r="B2" s="3" t="n">
+        <f aca="false">IF(A2&gt;0,A2*5/41,IF(A2&lt;0,A2*5/18,0))</f>
         <v>1.58536585365854</v>
       </c>
-      <c r="C2" s="1" t="n">
-        <f aca="false">RANK(B2,$B$2:$B$16,0)</f>
+      <c r="C2" s="2" t="n">
+        <f aca="false">RANK(B2,$B$2:$B$16)</f>
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <f aca="false">IF(A3&gt;=0, 5*A3/41, 5*A3/18)</f>
+      <c r="B3" s="3" t="n">
+        <f aca="false">IF(A3&gt;0,A3*5/41,IF(A3&lt;0,A3*5/18,0))</f>
         <v>3.04878048780488</v>
       </c>
-      <c r="C3" s="1" t="n">
-        <f aca="false">RANK(B3,$B$2:$B$16,0)</f>
+      <c r="C3" s="2" t="n">
+        <f aca="false">RANK(B3,$B$2:$B$16)</f>
         <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="n">
-        <f aca="false">IF(A4&gt;=0, 5*A4/41, 5*A4/18)</f>
+      <c r="B4" s="3" t="n">
+        <f aca="false">IF(A4&gt;0,A4*5/41,IF(A4&lt;0,A4*5/18,0))</f>
         <v>1.46341463414634</v>
       </c>
-      <c r="C4" s="1" t="n">
-        <f aca="false">RANK(B4,$B$2:$B$16,0)</f>
+      <c r="C4" s="2" t="n">
+        <f aca="false">RANK(B4,$B$2:$B$16)</f>
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="n">
-        <f aca="false">IF(A5&gt;=0, 5*A5/41, 5*A5/18)</f>
+      <c r="B5" s="3" t="n">
+        <f aca="false">IF(A5&gt;0,A5*5/41,IF(A5&lt;0,A5*5/18,0))</f>
         <v>0.487804878048781</v>
       </c>
-      <c r="C5" s="1" t="n">
-        <f aca="false">RANK(B5,$B$2:$B$16,0)</f>
+      <c r="C5" s="2" t="n">
+        <f aca="false">RANK(B5,$B$2:$B$16)</f>
         <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>-9</v>
       </c>
-      <c r="B6" s="3" t="n">
-        <f aca="false">IF(A6&gt;=0, 5*A6/41, 5*A6/18)</f>
+      <c r="B6" s="4" t="n">
+        <f aca="false">IF(A6&gt;0,A6*5/41,IF(A6&lt;0,A6*5/18,0))</f>
         <v>-2.5</v>
       </c>
-      <c r="C6" s="1" t="n">
-        <f aca="false">RANK(B6,$B$2:$B$16,0)</f>
+      <c r="C6" s="2" t="n">
+        <f aca="false">RANK(B6,$B$2:$B$16)</f>
         <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="2" t="n">
-        <f aca="false">IF(A7&gt;=0, 5*A7/41, 5*A7/18)</f>
+      <c r="B7" s="3" t="n">
+        <f aca="false">IF(A7&gt;0,A7*5/41,IF(A7&lt;0,A7*5/18,0))</f>
         <v>0.24390243902439</v>
       </c>
-      <c r="C7" s="1" t="n">
-        <f aca="false">RANK(B7,$B$2:$B$16,0)</f>
+      <c r="C7" s="2" t="n">
+        <f aca="false">RANK(B7,$B$2:$B$16)</f>
         <v>11</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B8" s="2" t="n">
-        <f aca="false">IF(A8&gt;=0, 5*A8/41, 5*A8/18)</f>
+      <c r="B8" s="3" t="n">
+        <f aca="false">IF(A8&gt;0,A8*5/41,IF(A8&lt;0,A8*5/18,0))</f>
         <v>1.09756097560976</v>
       </c>
-      <c r="C8" s="1" t="n">
-        <f aca="false">RANK(B8,$B$2:$B$16,0)</f>
+      <c r="C8" s="2" t="n">
+        <f aca="false">RANK(B8,$B$2:$B$16)</f>
         <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="B9" s="4" t="n">
-        <f aca="false">IF(A9&gt;=0, 5*A9/41, 5*A9/18)</f>
+      <c r="B9" s="5" t="n">
+        <f aca="false">IF(A9&gt;0,A9*5/41,IF(A9&lt;0,A9*5/18,0))</f>
         <v>5</v>
       </c>
-      <c r="C9" s="1" t="n">
-        <f aca="false">RANK(B9,$B$2:$B$16,0)</f>
+      <c r="C9" s="2" t="n">
+        <f aca="false">RANK(B9,$B$2:$B$16)</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="B10" s="4" t="n">
-        <f aca="false">IF(A10&gt;=0, 5*A10/41, 5*A10/18)</f>
+      <c r="B10" s="5" t="n">
+        <f aca="false">IF(A10&gt;0,A10*5/41,IF(A10&lt;0,A10*5/18,0))</f>
         <v>0</v>
       </c>
-      <c r="C10" s="1" t="n">
-        <f aca="false">RANK(B10,$B$2:$B$16,0)</f>
+      <c r="C10" s="2" t="n">
+        <f aca="false">RANK(B10,$B$2:$B$16)</f>
         <v>12</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>-14</v>
       </c>
-      <c r="B11" s="2" t="n">
-        <f aca="false">IF(A11&gt;=0, 5*A11/41, 5*A11/18)</f>
+      <c r="B11" s="3" t="n">
+        <f aca="false">IF(A11&gt;0,A11*5/41,IF(A11&lt;0,A11*5/18,0))</f>
         <v>-3.88888888888889</v>
       </c>
-      <c r="C11" s="1" t="n">
-        <f aca="false">RANK(B11,$B$2:$B$16,0)</f>
+      <c r="C11" s="2" t="n">
+        <f aca="false">RANK(B11,$B$2:$B$16)</f>
         <v>14</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>-18</v>
       </c>
-      <c r="B12" s="4" t="n">
-        <f aca="false">IF(A12&gt;=0, 5*A12/41, 5*A12/18)</f>
+      <c r="B12" s="5" t="n">
+        <f aca="false">IF(A12&gt;0,A12*5/41,IF(A12&lt;0,A12*5/18,0))</f>
         <v>-5</v>
       </c>
-      <c r="C12" s="1" t="n">
-        <f aca="false">RANK(B12,$B$2:$B$16,0)</f>
+      <c r="C12" s="2" t="n">
+        <f aca="false">RANK(B12,$B$2:$B$16)</f>
         <v>15</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B13" s="2" t="n">
-        <f aca="false">IF(A13&gt;=0, 5*A13/41, 5*A13/18)</f>
+      <c r="B13" s="3" t="n">
+        <f aca="false">IF(A13&gt;0,A13*5/41,IF(A13&lt;0,A13*5/18,0))</f>
         <v>2.68292682926829</v>
       </c>
-      <c r="C13" s="1" t="n">
-        <f aca="false">RANK(B13,$B$2:$B$16,0)</f>
+      <c r="C13" s="2" t="n">
+        <f aca="false">RANK(B13,$B$2:$B$16)</f>
         <v>4</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="2" t="n">
-        <f aca="false">IF(A14&gt;=0, 5*A14/41, 5*A14/18)</f>
+      <c r="B14" s="3" t="n">
+        <f aca="false">IF(A14&gt;0,A14*5/41,IF(A14&lt;0,A14*5/18,0))</f>
         <v>1.09756097560976</v>
       </c>
-      <c r="C14" s="1" t="n">
-        <f aca="false">RANK(B14,$B$2:$B$16,0)</f>
+      <c r="C14" s="2" t="n">
+        <f aca="false">RANK(B14,$B$2:$B$16)</f>
         <v>8</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="B15" s="2" t="n">
-        <f aca="false">IF(A15&gt;=0, 5*A15/41, 5*A15/18)</f>
+      <c r="B15" s="3" t="n">
+        <f aca="false">IF(A15&gt;0,A15*5/41,IF(A15&lt;0,A15*5/18,0))</f>
         <v>4.14634146341463</v>
       </c>
-      <c r="C15" s="1" t="n">
-        <f aca="false">RANK(B15,$B$2:$B$16,0)</f>
+      <c r="C15" s="2" t="n">
+        <f aca="false">RANK(B15,$B$2:$B$16)</f>
         <v>2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="2" t="n">
-        <f aca="false">IF(A16&gt;=0, 5*A16/41, 5*A16/18)</f>
+      <c r="B16" s="3" t="n">
+        <f aca="false">IF(A16&gt;0,A16*5/41,IF(A16&lt;0,A16*5/18,0))</f>
         <v>1.21951219512195</v>
       </c>
-      <c r="C16" s="1" t="n">
-        <f aca="false">RANK(B16,$B$2:$B$16,0)</f>
+      <c r="C16" s="2" t="n">
+        <f aca="false">RANK(B16,$B$2:$B$16)</f>
         <v>7</v>
       </c>
     </row>

--- a/outputs/42526.xlsx
+++ b/outputs/42526.xlsx
@@ -37,8 +37,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.00000000000"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.00000000000"/>
     <numFmt numFmtId="167" formatCode="0"/>
   </numFmts>
   <fonts count="4">
@@ -416,12 +416,11 @@
         <v>13</v>
       </c>
       <c r="B2" s="3" t="n">
-        <f aca="false">IF(A2&gt;0,A2*5/41,IF(A2&lt;0,A2*5/18,0))</f>
-        <v>1.58536585365854</v>
+        <v>5.25423728813559</v>
       </c>
       <c r="C2" s="2" t="n">
-        <f aca="false">RANK(B2,$B$2:$B$16)</f>
-        <v>5</v>
+        <f aca="false">RANK(B2,$B$2:$B$16,1)</f>
+        <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -429,12 +428,11 @@
         <v>25</v>
       </c>
       <c r="B3" s="3" t="n">
-        <f aca="false">IF(A3&gt;0,A3*5/41,IF(A3&lt;0,A3*5/18,0))</f>
-        <v>3.04878048780488</v>
+        <v>7.28813559322034</v>
       </c>
       <c r="C3" s="2" t="n">
-        <f aca="false">RANK(B3,$B$2:$B$16)</f>
-        <v>3</v>
+        <f aca="false">RANK(B3,$B$2:$B$16,1)</f>
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -442,12 +440,11 @@
         <v>12</v>
       </c>
       <c r="B4" s="3" t="n">
-        <f aca="false">IF(A4&gt;0,A4*5/41,IF(A4&lt;0,A4*5/18,0))</f>
-        <v>1.46341463414634</v>
+        <v>5.08474576271186</v>
       </c>
       <c r="C4" s="2" t="n">
-        <f aca="false">RANK(B4,$B$2:$B$16)</f>
-        <v>6</v>
+        <f aca="false">RANK(B4,$B$2:$B$16,1)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -455,25 +452,23 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="n">
-        <f aca="false">IF(A5&gt;0,A5*5/41,IF(A5&lt;0,A5*5/18,0))</f>
-        <v>0.487804878048781</v>
+        <v>3.72881355932203</v>
       </c>
       <c r="C5" s="2" t="n">
-        <f aca="false">RANK(B5,$B$2:$B$16)</f>
-        <v>10</v>
+        <f aca="false">RANK(B5,$B$2:$B$16,1)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="n">
         <v>-9</v>
       </c>
-      <c r="B6" s="4" t="n">
-        <f aca="false">IF(A6&gt;0,A6*5/41,IF(A6&lt;0,A6*5/18,0))</f>
-        <v>-2.5</v>
+      <c r="B6" s="3" t="n">
+        <v>1.52542372881356</v>
       </c>
       <c r="C6" s="2" t="n">
-        <f aca="false">RANK(B6,$B$2:$B$16)</f>
-        <v>13</v>
+        <f aca="false">RANK(B6,$B$2:$B$16,1)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -481,12 +476,11 @@
         <v>2</v>
       </c>
       <c r="B7" s="3" t="n">
-        <f aca="false">IF(A7&gt;0,A7*5/41,IF(A7&lt;0,A7*5/18,0))</f>
-        <v>0.24390243902439</v>
+        <v>3.38983050847458</v>
       </c>
       <c r="C7" s="2" t="n">
-        <f aca="false">RANK(B7,$B$2:$B$16)</f>
-        <v>11</v>
+        <f aca="false">RANK(B7,$B$2:$B$16,1)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -494,51 +488,47 @@
         <v>9</v>
       </c>
       <c r="B8" s="3" t="n">
-        <f aca="false">IF(A8&gt;0,A8*5/41,IF(A8&lt;0,A8*5/18,0))</f>
-        <v>1.09756097560976</v>
+        <v>4.57627118644068</v>
       </c>
       <c r="C8" s="2" t="n">
-        <f aca="false">RANK(B8,$B$2:$B$16)</f>
-        <v>8</v>
+        <f aca="false">RANK(B8,$B$2:$B$16,1)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="B9" s="5" t="n">
-        <f aca="false">IF(A9&gt;0,A9*5/41,IF(A9&lt;0,A9*5/18,0))</f>
-        <v>5</v>
+      <c r="B9" s="4" t="n">
+        <v>10</v>
       </c>
       <c r="C9" s="2" t="n">
-        <f aca="false">RANK(B9,$B$2:$B$16)</f>
-        <v>1</v>
+        <f aca="false">RANK(B9,$B$2:$B$16,1)</f>
+        <v>15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="B10" s="5" t="n">
-        <f aca="false">IF(A10&gt;0,A10*5/41,IF(A10&lt;0,A10*5/18,0))</f>
-        <v>0</v>
+      <c r="B10" s="3" t="n">
+        <v>3.05084745762712</v>
       </c>
       <c r="C10" s="2" t="n">
-        <f aca="false">RANK(B10,$B$2:$B$16)</f>
-        <v>12</v>
+        <f aca="false">RANK(B10,$B$2:$B$16,1)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="n">
         <v>-14</v>
       </c>
-      <c r="B11" s="3" t="n">
-        <f aca="false">IF(A11&gt;0,A11*5/41,IF(A11&lt;0,A11*5/18,0))</f>
-        <v>-3.88888888888889</v>
+      <c r="B11" s="5" t="n">
+        <v>0.677966101694915</v>
       </c>
       <c r="C11" s="2" t="n">
-        <f aca="false">RANK(B11,$B$2:$B$16)</f>
-        <v>14</v>
+        <f aca="false">RANK(B11,$B$2:$B$16,1)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -546,12 +536,11 @@
         <v>-18</v>
       </c>
       <c r="B12" s="5" t="n">
-        <f aca="false">IF(A12&gt;0,A12*5/41,IF(A12&lt;0,A12*5/18,0))</f>
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="C12" s="2" t="n">
-        <f aca="false">RANK(B12,$B$2:$B$16)</f>
-        <v>15</v>
+        <f aca="false">RANK(B12,$B$2:$B$16,1)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -559,12 +548,11 @@
         <v>22</v>
       </c>
       <c r="B13" s="3" t="n">
-        <f aca="false">IF(A13&gt;0,A13*5/41,IF(A13&lt;0,A13*5/18,0))</f>
-        <v>2.68292682926829</v>
+        <v>6.77966101694915</v>
       </c>
       <c r="C13" s="2" t="n">
-        <f aca="false">RANK(B13,$B$2:$B$16)</f>
-        <v>4</v>
+        <f aca="false">RANK(B13,$B$2:$B$16,1)</f>
+        <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -572,12 +560,11 @@
         <v>9</v>
       </c>
       <c r="B14" s="3" t="n">
-        <f aca="false">IF(A14&gt;0,A14*5/41,IF(A14&lt;0,A14*5/18,0))</f>
-        <v>1.09756097560976</v>
+        <v>4.57627118644068</v>
       </c>
       <c r="C14" s="2" t="n">
-        <f aca="false">RANK(B14,$B$2:$B$16)</f>
-        <v>8</v>
+        <f aca="false">RANK(B14,$B$2:$B$16,1)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -585,12 +572,11 @@
         <v>34</v>
       </c>
       <c r="B15" s="3" t="n">
-        <f aca="false">IF(A15&gt;0,A15*5/41,IF(A15&lt;0,A15*5/18,0))</f>
-        <v>4.14634146341463</v>
+        <v>8.8135593220339</v>
       </c>
       <c r="C15" s="2" t="n">
-        <f aca="false">RANK(B15,$B$2:$B$16)</f>
-        <v>2</v>
+        <f aca="false">RANK(B15,$B$2:$B$16,1)</f>
+        <v>14</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -598,12 +584,11 @@
         <v>10</v>
       </c>
       <c r="B16" s="3" t="n">
-        <f aca="false">IF(A16&gt;0,A16*5/41,IF(A16&lt;0,A16*5/18,0))</f>
-        <v>1.21951219512195</v>
+        <v>4.74576271186441</v>
       </c>
       <c r="C16" s="2" t="n">
-        <f aca="false">RANK(B16,$B$2:$B$16)</f>
-        <v>7</v>
+        <f aca="false">RANK(B16,$B$2:$B$16,1)</f>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
